--- a/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T0DEFC87B-000001</x:t>
+    <x:t>T8485D9B2-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T8485D9B2-000001</x:t>
+    <x:t>T63DD1B48-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T63DD1B48-000001</x:t>
+    <x:t>TBB71B753-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TBB71B753-000001</x:t>
+    <x:t>T494E8979-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T494E8979-000001</x:t>
+    <x:t>T575D5C16-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T575D5C16-000001</x:t>
+    <x:t>T4C4B7FEB-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T4C4B7FEB-000001</x:t>
+    <x:t>T23CBA7EC-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T23CBA7EC-000001</x:t>
+    <x:t>T5A160ADA-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T5A160ADA-000001</x:t>
+    <x:t>T8D74737A-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T8D74737A-000001</x:t>
+    <x:t>TA9BA3407-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-received-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TA9BA3407-000001</x:t>
+    <x:t>TF87918CC-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
